--- a/data/trans_orig/P21D_3_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D_3_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos en 2023</t>
+          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4541</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1246</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3880</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4227</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229405</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>334054</t>
+          <t>333393</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564584</t>
+          <t>564510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1113152</t>
+          <t>1113190</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>932970</t>
+          <t>933886</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2049221</t>
+          <t>2049172</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,97 +1416,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1569</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308317</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>620902</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>761</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1653661</t>
+          <t>1653639</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1581823</t>
+          <t>1581898</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1586977</t>
+          <t>1586982</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3238563</t>
+          <t>3238737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3244955</t>
+          <t>3244966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">

--- a/data/trans_orig/P21D_3_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D_3_R-Estudios-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>336688</t>
+          <t>363102</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333393</t>
+          <t>360036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>364366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>567565</t>
+          <t>616757</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564510</t>
+          <t>613356</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568811</t>
+          <t>618021</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>364366</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>364366</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>364366</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>568811</t>
+          <t>618021</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>568811</t>
+          <t>618021</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>568811</t>
+          <t>618021</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1116369</t>
+          <t>958763</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1113190</t>
+          <t>955685</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,17 +1216,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>936546</t>
+          <t>984770</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>933886</t>
+          <t>981780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2052915</t>
+          <t>1943533</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2049172</t>
+          <t>1939701</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,22 +1824,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -1867,17 +1867,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1657429</t>
+          <t>1559627</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1653639</t>
+          <t>1556594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1585521</t>
+          <t>1690111</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1581898</t>
+          <t>1686586</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1586982</t>
+          <t>1691563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3242949</t>
+          <t>3249739</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3238737</t>
+          <t>3246105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3244966</t>
+          <t>3251797</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1587534</t>
+          <t>1692124</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1587534</t>
+          <t>1692124</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1587534</t>
+          <t>1692124</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3245727</t>
+          <t>3252498</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3245727</t>
+          <t>3252498</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3245727</t>
+          <t>3252498</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
